--- a/docs/downloads/04/tbl_other_educ_sex_marovoay_bepako.xlsx
+++ b/docs/downloads/04/tbl_other_educ_sex_marovoay_bepako.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,10 +398,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -463,14 +463,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="6">
@@ -481,19 +481,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="E6">
-        <v>0.4</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="7">
@@ -509,14 +509,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D7">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="8">
@@ -532,14 +532,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D8">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>45.5</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -555,14 +555,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D9">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E9">
-        <v>9.699999999999999</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="10">
@@ -571,62 +571,56 @@
           <t>Marovoay - Bepako</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>9</v>
-      </c>
-      <c r="E10">
-        <v>5.8</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>282</v>
       </c>
       <c r="E11">
-        <v>1.9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>521</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="13">
@@ -642,14 +636,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D13">
-        <v>310</v>
+        <v>179</v>
       </c>
       <c r="E13">
-        <v>29.6</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="14">
@@ -665,14 +659,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D14">
-        <v>521</v>
+        <v>64</v>
       </c>
       <c r="E14">
-        <v>49.8</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="15">
@@ -683,19 +677,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D15">
-        <v>179</v>
+        <v>272</v>
       </c>
       <c r="E15">
-        <v>17.1</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="16">
@@ -706,19 +700,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D16">
-        <v>31</v>
+        <v>333</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="17">
@@ -729,19 +723,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="E17">
-        <v>0.5</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="18">
@@ -757,14 +751,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D18">
-        <v>297</v>
+        <v>49</v>
       </c>
       <c r="E18">
-        <v>40.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="19">
@@ -773,21 +767,10 @@
           <t>Marovoay - Tous</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>333</v>
-      </c>
-      <c r="E19">
-        <v>45.6</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -796,103 +779,10 @@
           <t>Marovoay - Tous</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>76</v>
-      </c>
-      <c r="E20">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>19</v>
-      </c>
-      <c r="E21">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>5</v>
-      </c>
-      <c r="E22">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24">
-        <v>50</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_other_educ_sex_marovoay_bepako.xlsx
+++ b/docs/downloads/04/tbl_other_educ_sex_marovoay_bepako.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,10 +398,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
@@ -417,14 +417,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D3">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="E3">
-        <v>46.7</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="4">
@@ -440,14 +440,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D4">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="E4">
-        <v>19.8</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="5">
@@ -463,14 +463,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="E5">
-        <v>10.5</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="6">
@@ -481,19 +481,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D6">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>33.1</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="7">
@@ -509,14 +509,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D7">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>45.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -532,14 +532,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D8">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E8">
-        <v>9.699999999999999</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="9">
@@ -555,14 +555,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D9">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E9">
-        <v>11.7</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="10">
@@ -571,56 +571,56 @@
           <t>Marovoay - Bepako</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>Secondaire 1er cycle</t>
         </is>
+      </c>
+      <c r="D10">
+        <v>15</v>
+      </c>
+      <c r="E10">
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D11">
-        <v>282</v>
+        <v>18</v>
       </c>
       <c r="E11">
-        <v>27</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Femme</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>521</v>
-      </c>
-      <c r="E12">
-        <v>49.8</v>
+          <t>Secondaire 1er cycle</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -636,14 +636,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D13">
-        <v>179</v>
+        <v>27</v>
       </c>
       <c r="E13">
-        <v>17.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -659,14 +659,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="D14">
-        <v>64</v>
+        <v>255</v>
       </c>
       <c r="E14">
-        <v>6.1</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="15">
@@ -677,19 +677,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D15">
-        <v>272</v>
+        <v>521</v>
       </c>
       <c r="E15">
-        <v>37.3</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="16">
@@ -700,19 +700,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="D16">
-        <v>333</v>
+        <v>179</v>
       </c>
       <c r="E16">
-        <v>45.6</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="17">
@@ -723,19 +723,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D17">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E17">
-        <v>10.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="18">
@@ -751,14 +751,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="D18">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E18">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="19">
@@ -767,10 +767,21 @@
           <t>Marovoay - Tous</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>232</v>
+      </c>
+      <c r="E19">
+        <v>31.8</v>
       </c>
     </row>
     <row r="20">
@@ -779,7 +790,88 @@
           <t>Marovoay - Tous</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>333</v>
+      </c>
+      <c r="E20">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>76</v>
+      </c>
+      <c r="E21">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>49</v>
+      </c>
+      <c r="E22">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
